--- a/144/DQ Templates and Instructions/Topic 1 DQ 2/Topic 1 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 1 DQ 2/Topic 1 DQ 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 1 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="566" documentId="8_{F0DFF4ED-F49F-4D0C-BB64-AFBFCD3897EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A18207D-934B-42BD-866B-3D2197FCB2AD}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="8_{F0DFF4ED-F49F-4D0C-BB64-AFBFCD3897EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{872B22C2-340C-4A36-A8BA-3E99E145BC92}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA857894-CCDD-4590-8F7E-A65A6A8D0808}"/>
   </bookViews>
@@ -43,6 +43,51 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={BC060AFA-39C1-44A6-A9ED-0E8A9C142FF5}</author>
+    <author>tc={F37EA718-B0ED-4ADE-A2DB-AD85E9256E58}</author>
+    <author>tc={E9BFACFB-8854-44EA-9A2A-E08DC1CB4A30}</author>
+    <author>tc={B580BE12-F9C1-42C1-B07D-8DBA81107F12}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{BC060AFA-39C1-44A6-A9ED-0E8A9C142FF5}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/fc444b5c3f9c4a248a148f1f65b6f4c9?sid=0ff7d3af-65cb-4d1e-bbd9-0ff57e8b91f0</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="1" shapeId="0" xr:uid="{F37EA718-B0ED-4ADE-A2DB-AD85E9256E58}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/4e999e54029a43d8b7b58d21e26817f7?sid=a1a57bba-9bd0-4ab2-994a-0c2b2c65ef01</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="2" shapeId="0" xr:uid="{E9BFACFB-8854-44EA-9A2A-E08DC1CB4A30}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://youtu.be/F4t2iY8rNVI?si=5lZh2IiOO883K12M</t>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="3" shapeId="0" xr:uid="{B580BE12-F9C1-42C1-B07D-8DBA81107F12}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/7475cd73cfcf47f884d86c351a977716?sid=2182524d-6ccc-44ad-993e-a1e541e670c8</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
@@ -387,7 +432,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -482,6 +527,18 @@
       <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="Baguet Script"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1076,6 +1133,14 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1102,6 +1167,186 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1203,186 +1448,6 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1456,14 +1521,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1873,6 +1930,12 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Richard Ketchersid" id="{C4024158-5679-4750-B267-07ADC3DFF409}" userId="S::richard.ketchersid@gcu.edu::a14ec2f7-27bd-40c3-90d9-209834cdef57" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -2168,6 +2231,47 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-07-16T19:29:49.31" personId="{C4024158-5679-4750-B267-07ADC3DFF409}" id="{BC060AFA-39C1-44A6-A9ED-0E8A9C142FF5}">
+    <text>https://www.loom.com/share/fc444b5c3f9c4a248a148f1f65b6f4c9?sid=0ff7d3af-65cb-4d1e-bbd9-0ff57e8b91f0</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>372693160</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/fc444b5c3f9c4a248a148f1f65b6f4c9?sid=0ff7d3af-65cb-4d1e-bbd9-0ff57e8b91f0"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="I2" dT="2026-07-16T19:31:27.70" personId="{C4024158-5679-4750-B267-07ADC3DFF409}" id="{F37EA718-B0ED-4ADE-A2DB-AD85E9256E58}">
+    <text>https://www.loom.com/share/4e999e54029a43d8b7b58d21e26817f7?sid=a1a57bba-9bd0-4ab2-994a-0c2b2c65ef01</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>4210359309</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/4e999e54029a43d8b7b58d21e26817f7?sid=a1a57bba-9bd0-4ab2-994a-0c2b2c65ef01"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-07-16T19:31:12.11" personId="{C4024158-5679-4750-B267-07ADC3DFF409}" id="{E9BFACFB-8854-44EA-9A2A-E08DC1CB4A30}">
+    <text>https://youtu.be/F4t2iY8rNVI?si=5lZh2IiOO883K12M</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1250956705</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="48" url="https://youtu.be/F4t2iY8rNVI?si=5lZh2IiOO883K12M"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="I5" dT="2026-07-16T19:31:46.67" personId="{C4024158-5679-4750-B267-07ADC3DFF409}" id="{B580BE12-F9C1-42C1-B07D-8DBA81107F12}">
+    <text>https://www.loom.com/share/7475cd73cfcf47f884d86c351a977716?sid=2182524d-6ccc-44ad-993e-a1e541e670c8</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>2014995384</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/7475cd73cfcf47f884d86c351a977716?sid=2182524d-6ccc-44ad-993e-a1e541e670c8"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D8CC96E-0E65-43D0-8350-DB2754A29A16}">
   <dimension ref="B2:I12"/>
@@ -2181,58 +2285,58 @@
       <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="60"/>
     </row>
     <row r="4" spans="2:9" ht="30">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="60"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="63"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="58"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="60"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="63"/>
     </row>
     <row r="6" spans="2:9" ht="30">
       <c r="B6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="58"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="60"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="63"/>
     </row>
     <row r="7" spans="2:9" ht="30.75" thickBot="1">
       <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="61"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="63"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="66"/>
     </row>
     <row r="8" spans="2:9" ht="15.75" thickBot="1">
       <c r="B8" s="7"/>
@@ -2266,7 +2370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FDA598-8F75-47DB-A1EB-542124AF2F6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FDA598-8F75-47DB-A1EB-542124AF2F6A}">
   <dimension ref="A1:S69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2293,36 +2397,36 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1" thickBot="1"/>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="116" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="70"/>
-      <c r="I2" s="98" t="s">
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="118"/>
+      <c r="I2" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="100"/>
-      <c r="O2" s="109" t="s">
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="108"/>
+      <c r="O2" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="110"/>
+      <c r="P2" s="73"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1">
-      <c r="C3" s="71"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="73"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="103"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="121"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="110"/>
+      <c r="M3" s="111"/>
       <c r="O3" s="35" t="s">
         <v>13</v>
       </c>
@@ -2339,20 +2443,20 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="14.45" customHeight="1">
-      <c r="C5" s="98" t="s">
+      <c r="C5" s="106" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="100"/>
-      <c r="I5" s="98" t="s">
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="108"/>
+      <c r="I5" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="99"/>
-      <c r="M5" s="100"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="108"/>
       <c r="O5" s="39" t="s">
         <v>18</v>
       </c>
@@ -2361,16 +2465,16 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
-      <c r="C6" s="101"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="103"/>
-      <c r="I6" s="101"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="103"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="111"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="111"/>
       <c r="O6" s="40" t="s">
         <v>20</v>
       </c>
@@ -2387,13 +2491,13 @@
       </c>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1">
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="122" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="158" t="s">
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="55" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2406,123 +2510,123 @@
         <f>IF(LEN(F8)&lt;5,"Too Short","")</f>
         <v/>
       </c>
-      <c r="I9" s="89" t="s">
+      <c r="I9" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="J9" s="90"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="90"/>
-      <c r="M9" s="91"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
+      <c r="M9" s="88"/>
       <c r="O9" s="43">
         <v>15</v>
       </c>
-      <c r="P9" s="123" t="s">
+      <c r="P9" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="Q9" s="123"/>
-      <c r="R9" s="123"/>
-      <c r="S9" s="124"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="95"/>
+      <c r="S9" s="96"/>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1">
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="91"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="94"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="88"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="90"/>
+      <c r="L10" s="90"/>
+      <c r="M10" s="91"/>
       <c r="O10" s="44">
         <v>15</v>
       </c>
-      <c r="P10" s="125" t="s">
+      <c r="P10" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="Q10" s="125"/>
-      <c r="R10" s="125"/>
-      <c r="S10" s="126"/>
+      <c r="Q10" s="97"/>
+      <c r="R10" s="97"/>
+      <c r="S10" s="98"/>
     </row>
     <row r="11" spans="1:19" ht="18" customHeight="1" thickBot="1">
       <c r="A11" s="45"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="94"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="97"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="91"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="93"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="94"/>
       <c r="O11" s="46">
         <v>16</v>
       </c>
-      <c r="P11" s="127" t="s">
+      <c r="P11" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="Q11" s="127"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="128"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="99"/>
+      <c r="S11" s="100"/>
     </row>
     <row r="12" spans="1:19" ht="18" customHeight="1" thickBot="1">
       <c r="A12" s="47"/>
-      <c r="B12" s="92"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="94"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="91"/>
       <c r="O12" s="48">
         <v>16</v>
       </c>
-      <c r="P12" s="129" t="s">
+      <c r="P12" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" s="129"/>
-      <c r="R12" s="129"/>
-      <c r="S12" s="130"/>
+      <c r="Q12" s="101"/>
+      <c r="R12" s="101"/>
+      <c r="S12" s="102"/>
     </row>
     <row r="13" spans="1:19" ht="18" customHeight="1" thickBot="1">
       <c r="A13" s="45"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="97"/>
-      <c r="I13" s="111" t="s">
+      <c r="B13" s="92"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
+      <c r="I13" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="112"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="112"/>
-      <c r="M13" s="113"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1">
       <c r="A14" s="45"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="115"/>
-      <c r="M14" s="116"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="79"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="86"/>
+      <c r="C15" s="134"/>
       <c r="D15" s="49"/>
-      <c r="E15" s="85" t="s">
+      <c r="E15" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="86"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="115"/>
-      <c r="K15" s="115"/>
-      <c r="L15" s="115"/>
-      <c r="M15" s="116"/>
+      <c r="F15" s="134"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="78"/>
+      <c r="M15" s="79"/>
     </row>
     <row r="16" spans="1:19">
       <c r="B16" s="50" t="s">
@@ -2537,11 +2641,11 @@
       <c r="F16" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="114"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="115"/>
-      <c r="M16" s="116"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="79"/>
     </row>
     <row r="17" spans="2:14">
       <c r="B17" s="4" t="str">
@@ -2557,11 +2661,11 @@
         <v>Check F8</v>
       </c>
       <c r="F17" s="30"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="115"/>
-      <c r="M17" s="116"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="79"/>
     </row>
     <row r="18" spans="2:14">
       <c r="B18" s="2" t="str">
@@ -2577,11 +2681,11 @@
         <v>Check F8</v>
       </c>
       <c r="F18" s="30"/>
-      <c r="I18" s="114"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="116"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="78"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="78"/>
+      <c r="M18" s="79"/>
     </row>
     <row r="19" spans="2:14">
       <c r="B19" s="2" t="str">
@@ -2597,11 +2701,11 @@
         <v>Check F8</v>
       </c>
       <c r="F19" s="30"/>
-      <c r="I19" s="114"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="115"/>
-      <c r="L19" s="115"/>
-      <c r="M19" s="116"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="79"/>
     </row>
     <row r="20" spans="2:14">
       <c r="B20" s="2" t="str">
@@ -2617,11 +2721,11 @@
         <v>Check F8</v>
       </c>
       <c r="F20" s="30"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="116"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="79"/>
     </row>
     <row r="21" spans="2:14">
       <c r="B21" s="2" t="str">
@@ -2637,11 +2741,11 @@
         <v>Check F8</v>
       </c>
       <c r="F21" s="30"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="115"/>
-      <c r="K21" s="115"/>
-      <c r="L21" s="115"/>
-      <c r="M21" s="116"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="79"/>
     </row>
     <row r="22" spans="2:14" ht="15.75" thickBot="1">
       <c r="B22" s="3" t="str">
@@ -2657,11 +2761,11 @@
         <v>Check F8</v>
       </c>
       <c r="F22" s="30"/>
-      <c r="I22" s="114"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="115"/>
-      <c r="L22" s="115"/>
-      <c r="M22" s="116"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="78"/>
+      <c r="M22" s="79"/>
     </row>
     <row r="23" spans="2:14" ht="15.75" thickBot="1">
       <c r="E23" s="2" t="str">
@@ -2669,27 +2773,27 @@
         <v>Check F8</v>
       </c>
       <c r="F23" s="30"/>
-      <c r="I23" s="114"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="115"/>
-      <c r="L23" s="115"/>
-      <c r="M23" s="116"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="78"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="79"/>
     </row>
     <row r="24" spans="2:14" ht="15.75" thickBot="1">
-      <c r="B24" s="87" t="s">
+      <c r="B24" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="88"/>
+      <c r="C24" s="136"/>
       <c r="E24" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Check F8</v>
       </c>
       <c r="F24" s="30"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="119"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="81"/>
+      <c r="M24" s="82"/>
     </row>
     <row r="25" spans="2:14" ht="15.75" thickBot="1">
       <c r="B25" s="10"/>
@@ -2712,22 +2816,22 @@
         <v>Check F8</v>
       </c>
       <c r="F26" s="30"/>
-      <c r="H26" s="120" t="str">
+      <c r="H26" s="83" t="str">
         <f>IF(E9,"Check F3","Use your graph to approximate the stopping distance at a speed of  "&amp;(E25+E26)/2&amp;" m/s")</f>
         <v>Check F3</v>
       </c>
-      <c r="I26" s="121"/>
-      <c r="J26" s="121"/>
-      <c r="K26" s="121"/>
-      <c r="L26" s="121"/>
-      <c r="M26" s="122"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="85"/>
       <c r="N26" s="32"/>
     </row>
     <row r="27" spans="2:14" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B27" s="81" t="s">
+      <c r="B27" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="82"/>
+      <c r="C27" s="130"/>
       <c r="E27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Check F8</v>
@@ -2735,67 +2839,67 @@
       <c r="F27" s="30"/>
     </row>
     <row r="28" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B28" s="83"/>
-      <c r="C28" s="84"/>
-      <c r="E28" s="81" t="s">
+      <c r="B28" s="131"/>
+      <c r="C28" s="132"/>
+      <c r="E28" s="129" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="82"/>
-      <c r="H28" s="131" t="s">
+      <c r="F28" s="130"/>
+      <c r="H28" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="I28" s="132"/>
-      <c r="J28" s="132"/>
-      <c r="K28" s="132"/>
-      <c r="L28" s="132"/>
-      <c r="M28" s="132"/>
-      <c r="N28" s="133"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="105"/>
     </row>
     <row r="29" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="E29" s="83"/>
-      <c r="F29" s="84"/>
-      <c r="H29" s="106" t="s">
+      <c r="E29" s="131"/>
+      <c r="F29" s="132"/>
+      <c r="H29" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="I29" s="107"/>
-      <c r="J29" s="107"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
       <c r="K29" s="33"/>
-      <c r="L29" s="104" t="s">
+      <c r="L29" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="M29" s="104"/>
-      <c r="N29" s="105"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="68"/>
     </row>
     <row r="30" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B30" s="77" t="s">
+      <c r="B30" s="125" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="78"/>
-      <c r="H30" s="106" t="s">
+      <c r="C30" s="126"/>
+      <c r="H30" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="I30" s="107"/>
-      <c r="J30" s="107"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="108"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="71"/>
       <c r="M30" s="33"/>
       <c r="N30" s="54" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B31" s="79"/>
-      <c r="C31" s="80"/>
+      <c r="B31" s="127"/>
+      <c r="C31" s="128"/>
     </row>
     <row r="32" spans="2:14" ht="14.45" customHeight="1">
-      <c r="B32" s="64" t="s">
+      <c r="B32" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="65"/>
+      <c r="C32" s="113"/>
     </row>
     <row r="33" spans="2:3" ht="15.75" thickBot="1">
-      <c r="B33" s="66"/>
-      <c r="C33" s="67"/>
+      <c r="B33" s="114"/>
+      <c r="C33" s="115"/>
     </row>
     <row r="68" spans="5:5">
       <c r="E68" s="34" t="s">
@@ -2808,7 +2912,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jWYFzSQOqkNCTDeJO3aZpXEKOh3czzP1/h0fYSjZ0Rarja58Tiy+CQhokmrVEjgmJYwksyVJXQV6S1BMGHjrOA==" saltValue="F36l0IXs6y+lai78pz9OjQ==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="pFKseMRv4Ux6BBHj2jTKapFjGufTQ6z4aDoAXVnS4x8rKNaWISbuMIA+xtYWV3QRWhZMXUeTDGg10WS5GVtsGg==" saltValue="VUyIZQU0m2ypjcU4rETQpg==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <customSheetViews>
     <customSheetView guid="{1E6EB3EC-58F4-42D5-9462-6EAD6EC3491E}">
       <selection activeCell="G24" sqref="G24"/>
@@ -2817,6 +2921,18 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="26">
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="C2:G3"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="E28:F29"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B10:F13"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="C5:G6"/>
     <mergeCell ref="L29:N29"/>
     <mergeCell ref="H30:L30"/>
     <mergeCell ref="O2:P2"/>
@@ -2831,18 +2947,6 @@
     <mergeCell ref="I2:M3"/>
     <mergeCell ref="I5:M6"/>
     <mergeCell ref="H29:J29"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="C2:G3"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="E28:F29"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B10:F13"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="C5:G6"/>
   </mergeCells>
   <conditionalFormatting sqref="F9">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -2850,7 +2954,7 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C2:G3" r:id="rId2" display="Video for this." xr:uid="{BD5C7101-D7FE-4519-BCDD-60C638344AEE}"/>
+    <hyperlink ref="C2:G3" r:id="rId2" display="Video for this DQ" xr:uid="{BD5C7101-D7FE-4519-BCDD-60C638344AEE}"/>
     <hyperlink ref="I2:M3" r:id="rId3" display="Video on #SPILL! Error" xr:uid="{6ED5AB37-6FD6-4D2E-904A-1016E4D4A698}"/>
     <hyperlink ref="I5:M6" r:id="rId4" display="Scatter plot using online Excel" xr:uid="{4E04CA62-B451-4A43-8535-A8565032051F}"/>
     <hyperlink ref="C5:G6" r:id="rId5" display="Video on Autofill" xr:uid="{7EE831E3-D2DF-4260-911D-209F861CF2EA}"/>
@@ -2858,6 +2962,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
   <drawing r:id="rId7"/>
+  <legacyDrawing r:id="rId8"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -2905,48 +3010,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1">
-      <c r="B1" s="142" t="s">
+      <c r="B1" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" thickBot="1">
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
     </row>
     <row r="3" spans="1:15" ht="17.25" thickBot="1">
-      <c r="B3" s="143" t="s">
+      <c r="B3" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="145"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="148"/>
       <c r="F3" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1"/>
     <row r="5" spans="1:15" ht="14.45" customHeight="1">
-      <c r="B5" s="146" t="s">
+      <c r="B5" s="149" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="148"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="150"/>
+      <c r="E5" s="150"/>
+      <c r="F5" s="151"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="B6" s="149"/>
-      <c r="C6" s="150"/>
-      <c r="D6" s="150"/>
-      <c r="E6" s="150"/>
-      <c r="F6" s="151"/>
+      <c r="B6" s="152"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="154"/>
       <c r="I6" s="13" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=E17:E27*B26+B25"</f>
         <v>#N/A</v>
@@ -2957,22 +3062,22 @@
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="B7" s="149"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="151"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="154"/>
       <c r="I7" s="13" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B25+E17:E27*B26"</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B8" s="152"/>
-      <c r="C8" s="153"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153"/>
-      <c r="F8" s="154"/>
+      <c r="B8" s="155"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="157"/>
       <c r="I8" s="13" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B25+B26*E17:E27"</f>
         <v>#N/A</v>
@@ -2988,15 +3093,15 @@
       <c r="O9" s="15"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="B10" s="155" t="s">
+      <c r="B10" s="158" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="156"/>
+      <c r="C10" s="159"/>
       <c r="D10" s="16"/>
-      <c r="E10" s="155" t="s">
+      <c r="E10" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="156"/>
+      <c r="F10" s="159"/>
       <c r="I10" s="13" t="e">
         <f ca="1">OR(SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=E17:E27*B26+B25",SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B25+E17:E27*B26",SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B25+B26*E17:E27",SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B26*E17:E27+B25")</f>
         <v>#N/A</v>
@@ -3279,10 +3384,10 @@
       </c>
     </row>
     <row r="19" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B19" s="134" t="s">
+      <c r="B19" s="137" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="135"/>
+      <c r="C19" s="138"/>
       <c r="E19" s="23" t="str">
         <f>'Linear Fit'!E24</f>
         <v>Check F8</v>
@@ -3419,14 +3524,14 @@
       </c>
     </row>
     <row r="23" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B23" s="134" t="s">
+      <c r="B23" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="135"/>
-      <c r="E23" s="136" t="s">
+      <c r="C23" s="138"/>
+      <c r="E23" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="137"/>
+      <c r="F23" s="140"/>
       <c r="H23" s="13" t="b">
         <f ca="1">AND(H12:H22)</f>
         <v>0</v>
@@ -3437,10 +3542,10 @@
       </c>
     </row>
     <row r="24" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B24" s="140"/>
-      <c r="C24" s="141"/>
-      <c r="E24" s="138"/>
-      <c r="F24" s="139"/>
+      <c r="B24" s="143"/>
+      <c r="C24" s="144"/>
+      <c r="E24" s="141"/>
+      <c r="F24" s="142"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="NP8KfZBdrRoMbO4+6K5mYP0YLFWU9vooHr25DXKnzf2iWNfCPBeST5gJcYchWDz1uCvu2t4wrx5R4CXYPCjDLw==" saltValue="iJTkW+8OkP+1lMG5ccDKfw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -3468,1562 +3573,1562 @@
   <dimension ref="A1:W33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="5" width="9.28515625" style="159" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="159" bestFit="1" customWidth="1"/>
-    <col min="7" max="23" width="9.28515625" style="159" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="159"/>
+    <col min="1" max="5" width="9.28515625" style="56" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="56" bestFit="1" customWidth="1"/>
+    <col min="7" max="23" width="9.28515625" style="56" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="56"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="H1" s="159">
+      <c r="H1" s="56">
         <v>1</v>
       </c>
-      <c r="I1" s="159">
+      <c r="I1" s="56">
         <v>2</v>
       </c>
-      <c r="J1" s="159">
+      <c r="J1" s="56">
         <v>3</v>
       </c>
-      <c r="K1" s="159">
+      <c r="K1" s="56">
         <v>4</v>
       </c>
-      <c r="L1" s="159">
+      <c r="L1" s="56">
         <v>5</v>
       </c>
-      <c r="M1" s="159">
+      <c r="M1" s="56">
         <v>6</v>
       </c>
-      <c r="N1" s="159">
+      <c r="N1" s="56">
         <v>7</v>
       </c>
-      <c r="O1" s="159">
+      <c r="O1" s="56">
         <v>8</v>
       </c>
-      <c r="P1" s="159">
+      <c r="P1" s="56">
         <v>9</v>
       </c>
-      <c r="Q1" s="159">
+      <c r="Q1" s="56">
         <v>10</v>
       </c>
-      <c r="R1" s="159">
+      <c r="R1" s="56">
         <v>11</v>
       </c>
-      <c r="S1" s="159">
+      <c r="S1" s="56">
         <v>12</v>
       </c>
-      <c r="T1" s="159">
+      <c r="T1" s="56">
         <v>13</v>
       </c>
-      <c r="U1" s="159">
+      <c r="U1" s="56">
         <v>14</v>
       </c>
-      <c r="V1" s="159">
+      <c r="V1" s="56">
         <v>15</v>
       </c>
-      <c r="W1" s="159">
+      <c r="W1" s="56">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:23">
-      <c r="G2" s="159">
+      <c r="G2" s="56">
         <v>1</v>
       </c>
-      <c r="H2" s="159">
+      <c r="H2" s="56">
         <v>2</v>
       </c>
-      <c r="I2" s="159">
+      <c r="I2" s="56">
         <v>3</v>
       </c>
-      <c r="J2" s="159">
+      <c r="J2" s="56">
         <v>5</v>
       </c>
-      <c r="K2" s="159">
+      <c r="K2" s="56">
         <v>7</v>
       </c>
-      <c r="L2" s="159">
+      <c r="L2" s="56">
         <v>11</v>
       </c>
-      <c r="M2" s="159">
+      <c r="M2" s="56">
         <v>13</v>
       </c>
-      <c r="N2" s="159">
+      <c r="N2" s="56">
         <v>17</v>
       </c>
-      <c r="O2" s="159">
+      <c r="O2" s="56">
         <v>19</v>
       </c>
-      <c r="P2" s="159">
+      <c r="P2" s="56">
         <v>23</v>
       </c>
-      <c r="Q2" s="159">
+      <c r="Q2" s="56">
         <v>29</v>
       </c>
-      <c r="R2" s="159">
+      <c r="R2" s="56">
         <v>947</v>
       </c>
-      <c r="S2" s="159">
+      <c r="S2" s="56">
         <v>953</v>
       </c>
-      <c r="T2" s="159">
+      <c r="T2" s="56">
         <v>967</v>
       </c>
-      <c r="U2" s="159">
+      <c r="U2" s="56">
         <v>971</v>
       </c>
-      <c r="V2" s="159">
+      <c r="V2" s="56">
         <v>977</v>
       </c>
-      <c r="W2" s="159">
+      <c r="W2" s="56">
         <v>983</v>
       </c>
     </row>
     <row r="3" spans="1:23">
-      <c r="G3" s="159">
+      <c r="G3" s="56">
         <v>2</v>
       </c>
-      <c r="H3" s="159">
+      <c r="H3" s="56">
         <v>31</v>
       </c>
-      <c r="I3" s="159">
+      <c r="I3" s="56">
         <v>37</v>
       </c>
-      <c r="J3" s="159">
+      <c r="J3" s="56">
         <v>41</v>
       </c>
-      <c r="K3" s="159">
+      <c r="K3" s="56">
         <v>43</v>
       </c>
-      <c r="L3" s="159">
+      <c r="L3" s="56">
         <v>47</v>
       </c>
-      <c r="M3" s="159">
+      <c r="M3" s="56">
         <v>53</v>
       </c>
-      <c r="N3" s="159">
+      <c r="N3" s="56">
         <v>59</v>
       </c>
-      <c r="O3" s="159">
+      <c r="O3" s="56">
         <v>61</v>
       </c>
-      <c r="P3" s="159">
+      <c r="P3" s="56">
         <v>67</v>
       </c>
-      <c r="Q3" s="159">
+      <c r="Q3" s="56">
         <v>71</v>
       </c>
-      <c r="R3" s="159">
+      <c r="R3" s="56">
         <v>991</v>
       </c>
-      <c r="S3" s="159">
+      <c r="S3" s="56">
         <v>997</v>
       </c>
-      <c r="T3" s="159">
+      <c r="T3" s="56">
         <v>1009</v>
       </c>
-      <c r="U3" s="159">
+      <c r="U3" s="56">
         <v>1013</v>
       </c>
-      <c r="V3" s="159">
+      <c r="V3" s="56">
         <v>1019</v>
       </c>
-      <c r="W3" s="159">
+      <c r="W3" s="56">
         <v>1021</v>
       </c>
     </row>
     <row r="4" spans="1:23">
-      <c r="G4" s="159">
+      <c r="G4" s="56">
         <v>3</v>
       </c>
-      <c r="H4" s="159">
+      <c r="H4" s="56">
         <v>73</v>
       </c>
-      <c r="I4" s="159">
+      <c r="I4" s="56">
         <v>79</v>
       </c>
-      <c r="J4" s="159">
+      <c r="J4" s="56">
         <v>83</v>
       </c>
-      <c r="K4" s="159">
+      <c r="K4" s="56">
         <v>89</v>
       </c>
-      <c r="L4" s="159">
+      <c r="L4" s="56">
         <v>97</v>
       </c>
-      <c r="M4" s="159">
+      <c r="M4" s="56">
         <v>101</v>
       </c>
-      <c r="N4" s="159">
+      <c r="N4" s="56">
         <v>103</v>
       </c>
-      <c r="O4" s="159">
+      <c r="O4" s="56">
         <v>107</v>
       </c>
-      <c r="P4" s="159">
+      <c r="P4" s="56">
         <v>109</v>
       </c>
-      <c r="Q4" s="159">
+      <c r="Q4" s="56">
         <v>113</v>
       </c>
-      <c r="R4" s="159">
+      <c r="R4" s="56">
         <v>1031</v>
       </c>
-      <c r="S4" s="159">
+      <c r="S4" s="56">
         <v>1033</v>
       </c>
-      <c r="T4" s="159">
+      <c r="T4" s="56">
         <v>1039</v>
       </c>
-      <c r="U4" s="159">
+      <c r="U4" s="56">
         <v>1049</v>
       </c>
-      <c r="V4" s="159">
+      <c r="V4" s="56">
         <v>1051</v>
       </c>
-      <c r="W4" s="159">
+      <c r="W4" s="56">
         <v>1061</v>
       </c>
     </row>
     <row r="5" spans="1:23">
-      <c r="G5" s="159">
+      <c r="G5" s="56">
         <v>4</v>
       </c>
-      <c r="H5" s="159">
+      <c r="H5" s="56">
         <v>127</v>
       </c>
-      <c r="I5" s="159">
+      <c r="I5" s="56">
         <v>131</v>
       </c>
-      <c r="J5" s="159">
+      <c r="J5" s="56">
         <v>137</v>
       </c>
-      <c r="K5" s="159">
+      <c r="K5" s="56">
         <v>139</v>
       </c>
-      <c r="L5" s="159">
+      <c r="L5" s="56">
         <v>149</v>
       </c>
-      <c r="M5" s="159">
+      <c r="M5" s="56">
         <v>151</v>
       </c>
-      <c r="N5" s="159">
+      <c r="N5" s="56">
         <v>157</v>
       </c>
-      <c r="O5" s="159">
+      <c r="O5" s="56">
         <v>163</v>
       </c>
-      <c r="P5" s="159">
+      <c r="P5" s="56">
         <v>167</v>
       </c>
-      <c r="Q5" s="159">
+      <c r="Q5" s="56">
         <v>173</v>
       </c>
-      <c r="R5" s="159">
+      <c r="R5" s="56">
         <v>1993</v>
       </c>
-      <c r="S5" s="159">
+      <c r="S5" s="56">
         <v>1997</v>
       </c>
-      <c r="T5" s="159">
+      <c r="T5" s="56">
         <v>1999</v>
       </c>
-      <c r="U5" s="159">
+      <c r="U5" s="56">
         <v>2003</v>
       </c>
-      <c r="V5" s="159">
+      <c r="V5" s="56">
         <v>2011</v>
       </c>
-      <c r="W5" s="159">
+      <c r="W5" s="56">
         <v>2017</v>
       </c>
     </row>
     <row r="6" spans="1:23">
-      <c r="A6" s="159">
+      <c r="A6" s="56">
         <v>1</v>
       </c>
-      <c r="B6" s="159">
+      <c r="B6" s="56">
         <f>CODE(MID('Linear Fit'!F$8,A6,1))</f>
         <v>89</v>
       </c>
-      <c r="C6" s="159">
+      <c r="C6" s="56">
         <f>MOD(B6,16)</f>
         <v>9</v>
       </c>
-      <c r="D6" s="159">
+      <c r="D6" s="56">
         <f>MOD((B6-C6)/16,16)</f>
         <v>5</v>
       </c>
-      <c r="E6" s="159">
+      <c r="E6" s="56">
         <f ca="1">INDIRECT("R"&amp;(C6+1)&amp;"C"&amp;(D6+7),0)</f>
         <v>439</v>
       </c>
-      <c r="G6" s="159">
+      <c r="G6" s="56">
         <v>5</v>
       </c>
-      <c r="H6" s="159">
+      <c r="H6" s="56">
         <v>179</v>
       </c>
-      <c r="I6" s="159">
+      <c r="I6" s="56">
         <v>181</v>
       </c>
-      <c r="J6" s="159">
+      <c r="J6" s="56">
         <v>191</v>
       </c>
-      <c r="K6" s="159">
+      <c r="K6" s="56">
         <v>193</v>
       </c>
-      <c r="L6" s="159">
+      <c r="L6" s="56">
         <v>197</v>
       </c>
-      <c r="M6" s="159">
+      <c r="M6" s="56">
         <v>199</v>
       </c>
-      <c r="N6" s="159">
+      <c r="N6" s="56">
         <v>211</v>
       </c>
-      <c r="O6" s="159">
+      <c r="O6" s="56">
         <v>223</v>
       </c>
-      <c r="P6" s="159">
+      <c r="P6" s="56">
         <v>227</v>
       </c>
-      <c r="Q6" s="159">
+      <c r="Q6" s="56">
         <v>229</v>
       </c>
-      <c r="R6" s="159">
+      <c r="R6" s="56">
         <v>2063</v>
       </c>
-      <c r="S6" s="159">
+      <c r="S6" s="56">
         <v>2069</v>
       </c>
-      <c r="T6" s="159">
+      <c r="T6" s="56">
         <v>2081</v>
       </c>
-      <c r="U6" s="159">
+      <c r="U6" s="56">
         <v>2083</v>
       </c>
-      <c r="V6" s="159">
+      <c r="V6" s="56">
         <v>2087</v>
       </c>
-      <c r="W6" s="159">
+      <c r="W6" s="56">
         <v>2089</v>
       </c>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="159">
+      <c r="A7" s="56">
         <v>2</v>
       </c>
-      <c r="B7" s="159">
+      <c r="B7" s="56">
         <f>CODE(MID('Linear Fit'!F$8,A7,1))</f>
         <v>111</v>
       </c>
-      <c r="C7" s="159">
+      <c r="C7" s="56">
         <f t="shared" ref="C7:C10" si="0">MOD(B7,16)</f>
         <v>15</v>
       </c>
-      <c r="D7" s="159">
+      <c r="D7" s="56">
         <f t="shared" ref="D7:D10" si="1">MOD((B7-C7)/16,16)</f>
         <v>6</v>
       </c>
-      <c r="E7" s="159">
+      <c r="E7" s="56">
         <f t="shared" ref="E7:E10" ca="1" si="2">INDIRECT("R"&amp;(C7+1)&amp;"C"&amp;(D7+7),0)</f>
         <v>839</v>
       </c>
-      <c r="G7" s="159">
+      <c r="G7" s="56">
         <v>6</v>
       </c>
-      <c r="H7" s="159">
+      <c r="H7" s="56">
         <v>233</v>
       </c>
-      <c r="I7" s="159">
+      <c r="I7" s="56">
         <v>239</v>
       </c>
-      <c r="J7" s="159">
+      <c r="J7" s="56">
         <v>241</v>
       </c>
-      <c r="K7" s="159">
+      <c r="K7" s="56">
         <v>251</v>
       </c>
-      <c r="L7" s="159">
+      <c r="L7" s="56">
         <v>257</v>
       </c>
-      <c r="M7" s="159">
+      <c r="M7" s="56">
         <v>263</v>
       </c>
-      <c r="N7" s="159">
+      <c r="N7" s="56">
         <v>269</v>
       </c>
-      <c r="O7" s="159">
+      <c r="O7" s="56">
         <v>271</v>
       </c>
-      <c r="P7" s="159">
+      <c r="P7" s="56">
         <v>277</v>
       </c>
-      <c r="Q7" s="159">
+      <c r="Q7" s="56">
         <v>281</v>
       </c>
-      <c r="R7" s="159">
+      <c r="R7" s="56">
         <v>2131</v>
       </c>
-      <c r="S7" s="159">
+      <c r="S7" s="56">
         <v>2137</v>
       </c>
-      <c r="T7" s="159">
+      <c r="T7" s="56">
         <v>2141</v>
       </c>
-      <c r="U7" s="159">
+      <c r="U7" s="56">
         <v>2143</v>
       </c>
-      <c r="V7" s="159">
+      <c r="V7" s="56">
         <v>2153</v>
       </c>
-      <c r="W7" s="159">
+      <c r="W7" s="56">
         <v>2161</v>
       </c>
     </row>
     <row r="8" spans="1:23">
-      <c r="A8" s="159">
+      <c r="A8" s="56">
         <v>3</v>
       </c>
-      <c r="B8" s="159">
+      <c r="B8" s="56">
         <f>CODE(MID('Linear Fit'!F$8,A8,1))</f>
         <v>117</v>
       </c>
-      <c r="C8" s="159">
+      <c r="C8" s="56">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D8" s="159">
+      <c r="D8" s="56">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="E8" s="159">
+      <c r="E8" s="56">
         <f t="shared" ca="1" si="2"/>
         <v>211</v>
       </c>
-      <c r="G8" s="159">
+      <c r="G8" s="56">
         <v>7</v>
       </c>
-      <c r="H8" s="159">
+      <c r="H8" s="56">
         <v>283</v>
       </c>
-      <c r="I8" s="159">
+      <c r="I8" s="56">
         <v>293</v>
       </c>
-      <c r="J8" s="159">
+      <c r="J8" s="56">
         <v>307</v>
       </c>
-      <c r="K8" s="159">
+      <c r="K8" s="56">
         <v>311</v>
       </c>
-      <c r="L8" s="159">
+      <c r="L8" s="56">
         <v>313</v>
       </c>
-      <c r="M8" s="159">
+      <c r="M8" s="56">
         <v>317</v>
       </c>
-      <c r="N8" s="159">
+      <c r="N8" s="56">
         <v>331</v>
       </c>
-      <c r="O8" s="159">
+      <c r="O8" s="56">
         <v>337</v>
       </c>
-      <c r="P8" s="159">
+      <c r="P8" s="56">
         <v>347</v>
       </c>
-      <c r="Q8" s="159">
+      <c r="Q8" s="56">
         <v>349</v>
       </c>
-      <c r="R8" s="159">
+      <c r="R8" s="56">
         <v>2221</v>
       </c>
-      <c r="S8" s="159">
+      <c r="S8" s="56">
         <v>2237</v>
       </c>
-      <c r="T8" s="159">
+      <c r="T8" s="56">
         <v>2239</v>
       </c>
-      <c r="U8" s="159">
+      <c r="U8" s="56">
         <v>2243</v>
       </c>
-      <c r="V8" s="159">
+      <c r="V8" s="56">
         <v>2251</v>
       </c>
-      <c r="W8" s="159">
+      <c r="W8" s="56">
         <v>2267</v>
       </c>
     </row>
     <row r="9" spans="1:23">
-      <c r="A9" s="159">
+      <c r="A9" s="56">
         <v>4</v>
       </c>
-      <c r="B9" s="159">
+      <c r="B9" s="56">
         <f>CODE(MID('Linear Fit'!F$8,A9,1))</f>
         <v>114</v>
       </c>
-      <c r="C9" s="159">
+      <c r="C9" s="56">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D9" s="159">
+      <c r="D9" s="56">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="E9" s="159">
+      <c r="E9" s="56">
         <f t="shared" ca="1" si="2"/>
         <v>59</v>
       </c>
-      <c r="G9" s="159">
+      <c r="G9" s="56">
         <v>8</v>
       </c>
-      <c r="H9" s="159">
+      <c r="H9" s="56">
         <v>353</v>
       </c>
-      <c r="I9" s="159">
+      <c r="I9" s="56">
         <v>359</v>
       </c>
-      <c r="J9" s="159">
+      <c r="J9" s="56">
         <v>367</v>
       </c>
-      <c r="K9" s="159">
+      <c r="K9" s="56">
         <v>373</v>
       </c>
-      <c r="L9" s="159">
+      <c r="L9" s="56">
         <v>379</v>
       </c>
-      <c r="M9" s="159">
+      <c r="M9" s="56">
         <v>383</v>
       </c>
-      <c r="N9" s="159">
+      <c r="N9" s="56">
         <v>389</v>
       </c>
-      <c r="O9" s="159">
+      <c r="O9" s="56">
         <v>397</v>
       </c>
-      <c r="P9" s="159">
+      <c r="P9" s="56">
         <v>401</v>
       </c>
-      <c r="Q9" s="159">
+      <c r="Q9" s="56">
         <v>409</v>
       </c>
-      <c r="R9" s="159">
+      <c r="R9" s="56">
         <v>2293</v>
       </c>
-      <c r="S9" s="159">
+      <c r="S9" s="56">
         <v>2297</v>
       </c>
-      <c r="T9" s="159">
+      <c r="T9" s="56">
         <v>2309</v>
       </c>
-      <c r="U9" s="159">
+      <c r="U9" s="56">
         <v>2311</v>
       </c>
-      <c r="V9" s="159">
+      <c r="V9" s="56">
         <v>2333</v>
       </c>
-      <c r="W9" s="159">
+      <c r="W9" s="56">
         <v>2339</v>
       </c>
     </row>
     <row r="10" spans="1:23">
-      <c r="A10" s="159">
+      <c r="A10" s="56">
         <v>5</v>
       </c>
-      <c r="B10" s="159">
+      <c r="B10" s="56">
         <f>CODE(MID('Linear Fit'!F$8,A10,1))</f>
         <v>32</v>
       </c>
-      <c r="C10" s="159">
+      <c r="C10" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D10" s="159">
+      <c r="D10" s="56">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E10" s="159">
+      <c r="E10" s="56">
         <f t="shared" ca="1" si="2"/>
         <v>2</v>
       </c>
-      <c r="G10" s="159">
+      <c r="G10" s="56">
         <v>9</v>
       </c>
-      <c r="H10" s="159">
+      <c r="H10" s="56">
         <v>419</v>
       </c>
-      <c r="I10" s="159">
+      <c r="I10" s="56">
         <v>421</v>
       </c>
-      <c r="J10" s="159">
+      <c r="J10" s="56">
         <v>431</v>
       </c>
-      <c r="K10" s="159">
+      <c r="K10" s="56">
         <v>433</v>
       </c>
-      <c r="L10" s="159">
+      <c r="L10" s="56">
         <v>439</v>
       </c>
-      <c r="M10" s="159">
+      <c r="M10" s="56">
         <v>443</v>
       </c>
-      <c r="N10" s="159">
+      <c r="N10" s="56">
         <v>449</v>
       </c>
-      <c r="O10" s="159">
+      <c r="O10" s="56">
         <v>457</v>
       </c>
-      <c r="P10" s="159">
+      <c r="P10" s="56">
         <v>461</v>
       </c>
-      <c r="Q10" s="159">
+      <c r="Q10" s="56">
         <v>463</v>
       </c>
-      <c r="R10" s="159">
+      <c r="R10" s="56">
         <v>2371</v>
       </c>
-      <c r="S10" s="159">
+      <c r="S10" s="56">
         <v>2377</v>
       </c>
-      <c r="T10" s="159">
+      <c r="T10" s="56">
         <v>2381</v>
       </c>
-      <c r="U10" s="159">
+      <c r="U10" s="56">
         <v>2383</v>
       </c>
-      <c r="V10" s="159">
+      <c r="V10" s="56">
         <v>2389</v>
       </c>
-      <c r="W10" s="159">
+      <c r="W10" s="56">
         <v>2393</v>
       </c>
     </row>
     <row r="11" spans="1:23">
-      <c r="A11" s="159" t="s">
+      <c r="A11" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="159">
+      <c r="B11" s="56">
         <f ca="1">MOD(PRODUCT(E6:E10),F13)</f>
         <v>3778</v>
       </c>
-      <c r="F11" s="159">
+      <c r="F11" s="56">
         <v>1103515245</v>
       </c>
-      <c r="G11" s="159">
+      <c r="G11" s="56">
         <v>10</v>
       </c>
-      <c r="H11" s="159">
+      <c r="H11" s="56">
         <v>467</v>
       </c>
-      <c r="I11" s="159">
+      <c r="I11" s="56">
         <v>479</v>
       </c>
-      <c r="J11" s="159">
+      <c r="J11" s="56">
         <v>487</v>
       </c>
-      <c r="K11" s="159">
+      <c r="K11" s="56">
         <v>491</v>
       </c>
-      <c r="L11" s="159">
+      <c r="L11" s="56">
         <v>499</v>
       </c>
-      <c r="M11" s="159">
+      <c r="M11" s="56">
         <v>503</v>
       </c>
-      <c r="N11" s="159">
+      <c r="N11" s="56">
         <v>509</v>
       </c>
-      <c r="O11" s="159">
+      <c r="O11" s="56">
         <v>521</v>
       </c>
-      <c r="P11" s="159">
+      <c r="P11" s="56">
         <v>523</v>
       </c>
-      <c r="Q11" s="159">
+      <c r="Q11" s="56">
         <v>541</v>
       </c>
-      <c r="R11" s="159">
+      <c r="R11" s="56">
         <v>2437</v>
       </c>
-      <c r="S11" s="159">
+      <c r="S11" s="56">
         <v>2441</v>
       </c>
-      <c r="T11" s="159">
+      <c r="T11" s="56">
         <v>2447</v>
       </c>
-      <c r="U11" s="159">
+      <c r="U11" s="56">
         <v>2459</v>
       </c>
-      <c r="V11" s="159">
+      <c r="V11" s="56">
         <v>2467</v>
       </c>
-      <c r="W11" s="159">
+      <c r="W11" s="56">
         <v>2473</v>
       </c>
     </row>
     <row r="12" spans="1:23">
-      <c r="A12" s="159" t="s">
+      <c r="A12" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="159">
+      <c r="B12" s="56">
         <f ca="1">MOD(B11*F11+F12,F13)</f>
         <v>5331</v>
       </c>
-      <c r="C12" s="159">
+      <c r="C12" s="56">
         <f ca="1">MOD(B12,2)</f>
         <v>1</v>
       </c>
-      <c r="D12" s="159">
+      <c r="D12" s="56">
         <f ca="1">B12/F$13</f>
         <v>0.162689208984375</v>
       </c>
-      <c r="E12" s="159">
+      <c r="E12" s="56">
         <f ca="1">(IF(D12&lt;0.25,0,IF(D12&lt;0.5,1,IF(D12&lt;0.75,3,4)))+1)*IF(C12=1,1,-1)</f>
         <v>1</v>
       </c>
-      <c r="F12" s="159">
+      <c r="F12" s="56">
         <v>12345</v>
       </c>
-      <c r="G12" s="159">
+      <c r="G12" s="56">
         <v>11</v>
       </c>
-      <c r="H12" s="159">
+      <c r="H12" s="56">
         <v>547</v>
       </c>
-      <c r="I12" s="159">
+      <c r="I12" s="56">
         <v>557</v>
       </c>
-      <c r="J12" s="159">
+      <c r="J12" s="56">
         <v>563</v>
       </c>
-      <c r="K12" s="159">
+      <c r="K12" s="56">
         <v>569</v>
       </c>
-      <c r="L12" s="159">
+      <c r="L12" s="56">
         <v>571</v>
       </c>
-      <c r="M12" s="159">
+      <c r="M12" s="56">
         <v>577</v>
       </c>
-      <c r="N12" s="159">
+      <c r="N12" s="56">
         <v>587</v>
       </c>
-      <c r="O12" s="159">
+      <c r="O12" s="56">
         <v>593</v>
       </c>
-      <c r="P12" s="159">
+      <c r="P12" s="56">
         <v>599</v>
       </c>
-      <c r="Q12" s="159">
+      <c r="Q12" s="56">
         <v>601</v>
       </c>
-      <c r="R12" s="159">
+      <c r="R12" s="56">
         <v>2539</v>
       </c>
-      <c r="S12" s="159">
+      <c r="S12" s="56">
         <v>2543</v>
       </c>
-      <c r="T12" s="159">
+      <c r="T12" s="56">
         <v>2549</v>
       </c>
-      <c r="U12" s="159">
+      <c r="U12" s="56">
         <v>2551</v>
       </c>
-      <c r="V12" s="159">
+      <c r="V12" s="56">
         <v>2557</v>
       </c>
-      <c r="W12" s="159">
+      <c r="W12" s="56">
         <v>2579</v>
       </c>
     </row>
     <row r="13" spans="1:23">
-      <c r="A13" s="159" t="s">
+      <c r="A13" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="160">
+      <c r="B13" s="57">
         <f t="shared" ref="B13:B33" ca="1" si="3">MOD(B12*F$11+F$12,F$13)</f>
         <v>22544</v>
       </c>
-      <c r="C13" s="159">
+      <c r="C13" s="56">
         <f t="shared" ref="C13:C33" ca="1" si="4">IF(D13&lt;0.5,0,1)</f>
         <v>1</v>
       </c>
-      <c r="D13" s="159">
+      <c r="D13" s="56">
         <f t="shared" ref="D13:D33" ca="1" si="5">B13/F$13</f>
         <v>0.68798828125</v>
       </c>
-      <c r="E13" s="159">
+      <c r="E13" s="56">
         <f t="shared" ref="E13:E33" ca="1" si="6">(IF(D13&lt;0.25,0,IF(D13&lt;0.5,1,IF(D13&lt;0.75,3,4)))+1)*IF(C13=1,1,-1)</f>
         <v>4</v>
       </c>
-      <c r="F13" s="159">
+      <c r="F13" s="56">
         <v>32768</v>
       </c>
-      <c r="G13" s="159">
+      <c r="G13" s="56">
         <v>12</v>
       </c>
-      <c r="H13" s="159">
+      <c r="H13" s="56">
         <v>607</v>
       </c>
-      <c r="I13" s="159">
+      <c r="I13" s="56">
         <v>613</v>
       </c>
-      <c r="J13" s="159">
+      <c r="J13" s="56">
         <v>617</v>
       </c>
-      <c r="K13" s="159">
+      <c r="K13" s="56">
         <v>619</v>
       </c>
-      <c r="L13" s="159">
+      <c r="L13" s="56">
         <v>631</v>
       </c>
-      <c r="M13" s="159">
+      <c r="M13" s="56">
         <v>641</v>
       </c>
-      <c r="N13" s="159">
+      <c r="N13" s="56">
         <v>643</v>
       </c>
-      <c r="O13" s="159">
+      <c r="O13" s="56">
         <v>647</v>
       </c>
-      <c r="P13" s="159">
+      <c r="P13" s="56">
         <v>653</v>
       </c>
-      <c r="Q13" s="159">
+      <c r="Q13" s="56">
         <v>659</v>
       </c>
-      <c r="R13" s="159">
+      <c r="R13" s="56">
         <v>2621</v>
       </c>
-      <c r="S13" s="159">
+      <c r="S13" s="56">
         <v>2633</v>
       </c>
-      <c r="T13" s="159">
+      <c r="T13" s="56">
         <v>2647</v>
       </c>
-      <c r="U13" s="159">
+      <c r="U13" s="56">
         <v>2657</v>
       </c>
-      <c r="V13" s="159">
+      <c r="V13" s="56">
         <v>2659</v>
       </c>
-      <c r="W13" s="159">
+      <c r="W13" s="56">
         <v>2663</v>
       </c>
     </row>
     <row r="14" spans="1:23">
-      <c r="A14" s="159" t="s">
+      <c r="A14" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="160">
+      <c r="B14" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>3849</v>
       </c>
-      <c r="C14" s="159">
+      <c r="C14" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D14" s="159">
+      <c r="D14" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.117462158203125</v>
       </c>
-      <c r="E14" s="159">
+      <c r="E14" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
-      <c r="G14" s="159">
+      <c r="G14" s="56">
         <v>13</v>
       </c>
-      <c r="H14" s="159">
+      <c r="H14" s="56">
         <v>661</v>
       </c>
-      <c r="I14" s="159">
+      <c r="I14" s="56">
         <v>673</v>
       </c>
-      <c r="J14" s="159">
+      <c r="J14" s="56">
         <v>677</v>
       </c>
-      <c r="K14" s="159">
+      <c r="K14" s="56">
         <v>683</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="56">
         <v>691</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="56">
         <v>701</v>
       </c>
-      <c r="N14" s="159">
+      <c r="N14" s="56">
         <v>709</v>
       </c>
-      <c r="O14" s="159">
+      <c r="O14" s="56">
         <v>719</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="56">
         <v>727</v>
       </c>
-      <c r="Q14" s="159">
+      <c r="Q14" s="56">
         <v>733</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="56">
         <v>2689</v>
       </c>
-      <c r="S14" s="159">
+      <c r="S14" s="56">
         <v>2693</v>
       </c>
-      <c r="T14" s="159">
+      <c r="T14" s="56">
         <v>2699</v>
       </c>
-      <c r="U14" s="159">
+      <c r="U14" s="56">
         <v>2707</v>
       </c>
-      <c r="V14" s="159">
+      <c r="V14" s="56">
         <v>2711</v>
       </c>
-      <c r="W14" s="159">
+      <c r="W14" s="56">
         <v>2713</v>
       </c>
     </row>
     <row r="15" spans="1:23">
-      <c r="A15" s="159" t="s">
+      <c r="A15" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="160">
+      <c r="B15" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>21774</v>
       </c>
-      <c r="C15" s="159">
+      <c r="C15" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D15" s="159">
+      <c r="D15" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.66448974609375</v>
       </c>
-      <c r="E15" s="159">
+      <c r="E15" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="G15" s="159">
+      <c r="G15" s="56">
         <v>14</v>
       </c>
-      <c r="H15" s="159">
+      <c r="H15" s="56">
         <v>739</v>
       </c>
-      <c r="I15" s="159">
+      <c r="I15" s="56">
         <v>743</v>
       </c>
-      <c r="J15" s="159">
+      <c r="J15" s="56">
         <v>751</v>
       </c>
-      <c r="K15" s="159">
+      <c r="K15" s="56">
         <v>757</v>
       </c>
-      <c r="L15" s="159">
+      <c r="L15" s="56">
         <v>761</v>
       </c>
-      <c r="M15" s="159">
+      <c r="M15" s="56">
         <v>769</v>
       </c>
-      <c r="N15" s="159">
+      <c r="N15" s="56">
         <v>773</v>
       </c>
-      <c r="O15" s="159">
+      <c r="O15" s="56">
         <v>787</v>
       </c>
-      <c r="P15" s="159">
+      <c r="P15" s="56">
         <v>797</v>
       </c>
-      <c r="Q15" s="159">
+      <c r="Q15" s="56">
         <v>809</v>
       </c>
-      <c r="R15" s="159">
+      <c r="R15" s="56">
         <v>2749</v>
       </c>
-      <c r="S15" s="159">
+      <c r="S15" s="56">
         <v>2753</v>
       </c>
-      <c r="T15" s="159">
+      <c r="T15" s="56">
         <v>2767</v>
       </c>
-      <c r="U15" s="159">
+      <c r="U15" s="56">
         <v>2777</v>
       </c>
-      <c r="V15" s="159">
+      <c r="V15" s="56">
         <v>2789</v>
       </c>
-      <c r="W15" s="159">
+      <c r="W15" s="56">
         <v>2791</v>
       </c>
     </row>
     <row r="16" spans="1:23">
-      <c r="A16" s="159" t="s">
+      <c r="A16" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="160">
+      <c r="B16" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>11055</v>
       </c>
-      <c r="C16" s="159">
+      <c r="C16" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D16" s="159">
+      <c r="D16" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.337371826171875</v>
       </c>
-      <c r="E16" s="159">
+      <c r="E16" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-2</v>
       </c>
-      <c r="G16" s="159">
+      <c r="G16" s="56">
         <v>15</v>
       </c>
-      <c r="H16" s="159">
+      <c r="H16" s="56">
         <v>811</v>
       </c>
-      <c r="I16" s="159">
+      <c r="I16" s="56">
         <v>821</v>
       </c>
-      <c r="J16" s="159">
+      <c r="J16" s="56">
         <v>823</v>
       </c>
-      <c r="K16" s="159">
+      <c r="K16" s="56">
         <v>827</v>
       </c>
-      <c r="L16" s="159">
+      <c r="L16" s="56">
         <v>829</v>
       </c>
-      <c r="M16" s="159">
+      <c r="M16" s="56">
         <v>839</v>
       </c>
-      <c r="N16" s="159">
+      <c r="N16" s="56">
         <v>853</v>
       </c>
-      <c r="O16" s="159">
+      <c r="O16" s="56">
         <v>857</v>
       </c>
-      <c r="P16" s="159">
+      <c r="P16" s="56">
         <v>859</v>
       </c>
-      <c r="Q16" s="159">
+      <c r="Q16" s="56">
         <v>863</v>
       </c>
-      <c r="R16" s="159">
+      <c r="R16" s="56">
         <v>2833</v>
       </c>
-      <c r="S16" s="159">
+      <c r="S16" s="56">
         <v>2837</v>
       </c>
-      <c r="T16" s="159">
+      <c r="T16" s="56">
         <v>2843</v>
       </c>
-      <c r="U16" s="159">
+      <c r="U16" s="56">
         <v>2851</v>
       </c>
-      <c r="V16" s="159">
+      <c r="V16" s="56">
         <v>2857</v>
       </c>
-      <c r="W16" s="159">
+      <c r="W16" s="56">
         <v>2861</v>
       </c>
     </row>
     <row r="17" spans="1:23">
-      <c r="A17" s="159" t="s">
+      <c r="A17" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="160">
+      <c r="B17" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>25916</v>
       </c>
-      <c r="C17" s="159">
+      <c r="C17" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D17" s="159">
+      <c r="D17" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.7908935546875</v>
       </c>
-      <c r="E17" s="159">
+      <c r="E17" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>5</v>
       </c>
-      <c r="G17" s="159">
+      <c r="G17" s="56">
         <v>16</v>
       </c>
-      <c r="H17" s="159">
+      <c r="H17" s="56">
         <v>877</v>
       </c>
-      <c r="I17" s="159">
+      <c r="I17" s="56">
         <v>881</v>
       </c>
-      <c r="J17" s="159">
+      <c r="J17" s="56">
         <v>883</v>
       </c>
-      <c r="K17" s="159">
+      <c r="K17" s="56">
         <v>887</v>
       </c>
-      <c r="L17" s="159">
+      <c r="L17" s="56">
         <v>907</v>
       </c>
-      <c r="M17" s="159">
+      <c r="M17" s="56">
         <v>911</v>
       </c>
-      <c r="N17" s="159">
+      <c r="N17" s="56">
         <v>919</v>
       </c>
-      <c r="O17" s="159">
+      <c r="O17" s="56">
         <v>929</v>
       </c>
-      <c r="P17" s="159">
+      <c r="P17" s="56">
         <v>937</v>
       </c>
-      <c r="Q17" s="159">
+      <c r="Q17" s="56">
         <v>941</v>
       </c>
-      <c r="R17" s="159">
+      <c r="R17" s="56">
         <v>2909</v>
       </c>
-      <c r="S17" s="159">
+      <c r="S17" s="56">
         <v>2917</v>
       </c>
-      <c r="T17" s="159">
+      <c r="T17" s="56">
         <v>2927</v>
       </c>
-      <c r="U17" s="159">
+      <c r="U17" s="56">
         <v>2939</v>
       </c>
-      <c r="V17" s="159">
+      <c r="V17" s="56">
         <v>2953</v>
       </c>
-      <c r="W17" s="159">
+      <c r="W17" s="56">
         <v>2957</v>
       </c>
     </row>
     <row r="18" spans="1:23">
-      <c r="A18" s="159" t="s">
+      <c r="A18" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="160">
+      <c r="B18" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>4805</v>
       </c>
-      <c r="C18" s="159">
+      <c r="C18" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D18" s="159">
+      <c r="D18" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.146636962890625</v>
       </c>
-      <c r="E18" s="159">
+      <c r="E18" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:23">
-      <c r="A19" s="159" t="s">
+      <c r="A19" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="160">
+      <c r="B19" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>13338</v>
       </c>
-      <c r="C19" s="159">
+      <c r="C19" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D19" s="159">
+      <c r="D19" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.40704345703125</v>
       </c>
-      <c r="E19" s="159">
+      <c r="E19" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-2</v>
       </c>
     </row>
     <row r="20" spans="1:23">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="160">
+      <c r="B20" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>19275</v>
       </c>
-      <c r="C20" s="159">
+      <c r="C20" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D20" s="159">
+      <c r="D20" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.588226318359375</v>
       </c>
-      <c r="E20" s="159">
+      <c r="E20" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="H20" s="159">
+      <c r="H20" s="56">
         <f ca="1">10+SUM(E$12:E13)</f>
         <v>15</v>
       </c>
-      <c r="I20" s="159">
+      <c r="I20" s="56">
         <f ca="1">IF(H20&gt;=0,H20,-H20)</f>
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:23">
-      <c r="A21" s="159" t="s">
+      <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="160">
+      <c r="B21" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>6440</v>
       </c>
-      <c r="C21" s="159">
+      <c r="C21" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D21" s="159">
+      <c r="D21" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.196533203125</v>
       </c>
-      <c r="E21" s="159">
+      <c r="E21" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
-      <c r="H21" s="159">
+      <c r="H21" s="56">
         <f ca="1">10+SUM(E$12:E14)</f>
         <v>14</v>
       </c>
-      <c r="I21" s="159">
+      <c r="I21" s="56">
         <f t="shared" ref="I21:I29" ca="1" si="7">IF(H21&gt;=0,H21,-H21)</f>
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:23">
-      <c r="A22" s="159" t="s">
+      <c r="A22" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="160">
+      <c r="B22" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>5697</v>
       </c>
-      <c r="C22" s="159">
+      <c r="C22" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D22" s="159">
+      <c r="D22" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.173858642578125</v>
       </c>
-      <c r="E22" s="159">
+      <c r="E22" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
-      <c r="H22" s="159">
+      <c r="H22" s="56">
         <f ca="1">10+SUM(E$12:E15)</f>
         <v>18</v>
       </c>
-      <c r="I22" s="159">
+      <c r="I22" s="56">
         <f t="shared" ca="1" si="7"/>
         <v>18</v>
       </c>
-      <c r="M22" s="160"/>
+      <c r="M22" s="57"/>
     </row>
     <row r="23" spans="1:23">
-      <c r="A23" s="159" t="s">
+      <c r="A23" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="160">
+      <c r="B23" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>30694</v>
       </c>
-      <c r="C23" s="159">
+      <c r="C23" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D23" s="159">
+      <c r="D23" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.93670654296875</v>
       </c>
-      <c r="E23" s="159">
+      <c r="E23" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>5</v>
       </c>
-      <c r="H23" s="159">
+      <c r="H23" s="56">
         <f ca="1">10+SUM(E$12:E16)</f>
         <v>16</v>
       </c>
-      <c r="I23" s="159">
+      <c r="I23" s="56">
         <f t="shared" ca="1" si="7"/>
         <v>16</v>
       </c>
-      <c r="M23" s="160"/>
+      <c r="M23" s="57"/>
     </row>
     <row r="24" spans="1:23">
-      <c r="A24" s="159" t="s">
+      <c r="A24" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="160">
+      <c r="B24" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>20775</v>
       </c>
-      <c r="C24" s="159">
+      <c r="C24" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D24" s="159">
+      <c r="D24" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.634002685546875</v>
       </c>
-      <c r="E24" s="159">
+      <c r="E24" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="H24" s="159">
+      <c r="H24" s="56">
         <f ca="1">10+SUM(E$12:E17)</f>
         <v>21</v>
       </c>
-      <c r="I24" s="159">
+      <c r="I24" s="56">
         <f t="shared" ca="1" si="7"/>
         <v>21</v>
       </c>
-      <c r="M24" s="160"/>
+      <c r="M24" s="57"/>
     </row>
     <row r="25" spans="1:23">
-      <c r="A25" s="159" t="s">
+      <c r="A25" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="160">
+      <c r="B25" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>8148</v>
       </c>
-      <c r="C25" s="159">
+      <c r="C25" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D25" s="159">
+      <c r="D25" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.2486572265625</v>
       </c>
-      <c r="E25" s="159">
+      <c r="E25" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
-      <c r="H25" s="159">
+      <c r="H25" s="56">
         <f ca="1">10+SUM(E$12:E18)</f>
         <v>20</v>
       </c>
-      <c r="I25" s="159">
+      <c r="I25" s="56">
         <f t="shared" ca="1" si="7"/>
         <v>20</v>
       </c>
-      <c r="M25" s="160"/>
+      <c r="M25" s="57"/>
     </row>
     <row r="26" spans="1:23">
-      <c r="A26" s="159" t="s">
+      <c r="A26" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="160">
+      <c r="B26" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>21885</v>
       </c>
-      <c r="C26" s="159">
+      <c r="C26" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D26" s="159">
+      <c r="D26" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.667877197265625</v>
       </c>
-      <c r="E26" s="159">
+      <c r="E26" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="H26" s="159">
+      <c r="H26" s="56">
         <f ca="1">10+SUM(E$12:E19)</f>
         <v>18</v>
       </c>
-      <c r="I26" s="159">
+      <c r="I26" s="56">
         <f t="shared" ca="1" si="7"/>
         <v>18</v>
       </c>
-      <c r="M26" s="160"/>
+      <c r="M26" s="57"/>
     </row>
     <row r="27" spans="1:23">
-      <c r="A27" s="159" t="s">
+      <c r="A27" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="160">
+      <c r="B27" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>11378</v>
       </c>
-      <c r="C27" s="159">
+      <c r="C27" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D27" s="159">
+      <c r="D27" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.34722900390625</v>
       </c>
-      <c r="E27" s="159">
+      <c r="E27" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-2</v>
       </c>
-      <c r="H27" s="159">
+      <c r="H27" s="56">
         <f ca="1">10+SUM(E$12:E20)</f>
         <v>22</v>
       </c>
-      <c r="I27" s="159">
+      <c r="I27" s="56">
         <f t="shared" ca="1" si="7"/>
         <v>22</v>
       </c>
-      <c r="M27" s="160"/>
+      <c r="M27" s="57"/>
     </row>
     <row r="28" spans="1:23">
-      <c r="A28" s="159" t="s">
+      <c r="A28" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="160">
+      <c r="B28" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>22723</v>
       </c>
-      <c r="C28" s="159">
+      <c r="C28" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D28" s="159">
+      <c r="D28" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.693450927734375</v>
       </c>
-      <c r="E28" s="159">
+      <c r="E28" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="H28" s="159">
+      <c r="H28" s="56">
         <f ca="1">10+SUM(E$12:E21)</f>
         <v>21</v>
       </c>
-      <c r="I28" s="159">
+      <c r="I28" s="56">
         <f t="shared" ca="1" si="7"/>
         <v>21</v>
       </c>
-      <c r="M28" s="160"/>
+      <c r="M28" s="57"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="159" t="s">
+      <c r="A29" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="160">
+      <c r="B29" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>25920</v>
       </c>
-      <c r="C29" s="159">
+      <c r="C29" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D29" s="159">
+      <c r="D29" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.791015625</v>
       </c>
-      <c r="E29" s="159">
+      <c r="E29" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>5</v>
       </c>
-      <c r="H29" s="159">
+      <c r="H29" s="56">
         <f ca="1">10+SUM(E$12:E22)</f>
         <v>20</v>
       </c>
-      <c r="I29" s="159">
+      <c r="I29" s="56">
         <f t="shared" ca="1" si="7"/>
         <v>20</v>
       </c>
-      <c r="M29" s="160"/>
+      <c r="M29" s="57"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="159" t="s">
+      <c r="A30" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="160">
+      <c r="B30" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>19577</v>
       </c>
-      <c r="C30" s="159">
+      <c r="C30" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="D30" s="159">
+      <c r="D30" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.597442626953125</v>
       </c>
-      <c r="E30" s="159">
+      <c r="E30" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>4</v>
       </c>
-      <c r="M30" s="160"/>
+      <c r="M30" s="57"/>
     </row>
     <row r="31" spans="1:23">
-      <c r="A31" s="159" t="s">
+      <c r="A31" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="160">
+      <c r="B31" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>7614</v>
       </c>
-      <c r="C31" s="159">
+      <c r="C31" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D31" s="159">
+      <c r="D31" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.23236083984375</v>
       </c>
-      <c r="E31" s="159">
+      <c r="E31" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
-      <c r="M31" s="160"/>
+      <c r="M31" s="57"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="A32" s="159" t="s">
+      <c r="A32" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="160">
+      <c r="B32" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>15903</v>
       </c>
-      <c r="C32" s="159">
+      <c r="C32" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D32" s="159">
+      <c r="D32" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.485321044921875</v>
       </c>
-      <c r="E32" s="159">
+      <c r="E32" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-2</v>
       </c>
-      <c r="M32" s="160"/>
+      <c r="M32" s="57"/>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="159" t="s">
+      <c r="A33" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="160">
+      <c r="B33" s="57">
         <f t="shared" ca="1" si="3"/>
         <v>5484</v>
       </c>
-      <c r="C33" s="159">
+      <c r="C33" s="56">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="D33" s="159">
+      <c r="D33" s="56">
         <f t="shared" ca="1" si="5"/>
         <v>0.1673583984375</v>
       </c>
-      <c r="E33" s="159">
+      <c r="E33" s="56">
         <f t="shared" ca="1" si="6"/>
         <v>-1</v>
       </c>
-      <c r="M33" s="160"/>
+      <c r="M33" s="57"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="kIqIyQVbcPXGm24+FqtVMwNhQMraXxnC2cf2XxPdnOBUTPuVJbYj1BfMsq4OA0DOzsAdaBkyudqG50U8kadqjQ==" saltValue="UV69Rny4JSR9+pkbwlcXkg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -5043,54 +5148,54 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="5" spans="3:8">
-      <c r="C5" s="157" t="s">
+      <c r="C5" s="160" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
     </row>
     <row r="6" spans="3:8">
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
+      <c r="C6" s="160"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
     </row>
     <row r="7" spans="3:8">
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
     </row>
     <row r="8" spans="3:8">
-      <c r="C8" s="157"/>
-      <c r="D8" s="157"/>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="157"/>
-      <c r="H8" s="157"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="160"/>
     </row>
     <row r="9" spans="3:8">
-      <c r="C9" s="157"/>
-      <c r="D9" s="157"/>
-      <c r="E9" s="157"/>
-      <c r="F9" s="157"/>
-      <c r="G9" s="157"/>
-      <c r="H9" s="157"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
     </row>
     <row r="10" spans="3:8">
-      <c r="C10" s="157"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="157"/>
-      <c r="F10" s="157"/>
-      <c r="G10" s="157"/>
-      <c r="H10" s="157"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5102,12 +5207,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5328,19 +5434,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8613C9D7-E17F-4BAF-838C-91D0DFFDABBA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4AD473-4FA9-46C1-A1D3-2EA805B81A69}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5365,11 +5472,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4AD473-4FA9-46C1-A1D3-2EA805B81A69}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8613C9D7-E17F-4BAF-838C-91D0DFFDABBA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>